--- a/template/Projet_ODD_SIVARAJAH.xlsx
+++ b/template/Projet_ODD_SIVARAJAH.xlsx
@@ -12,6 +12,7 @@
     <sheet name="TCD" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Correlations" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CALC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TDB_1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,12 +31,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C0C0C0"/>
+        <bgColor rgb="00C0C0C0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,8 +57,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -126,6 +136,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblGenres" displayName="tblGenres" ref="A1:A3" headerRowCount="1">
+  <autoFilter ref="A1:A3"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fb20d332870&gt;"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblAges" displayName="tblAges" ref="C1:C8" headerRowCount="1">
+  <autoFilter ref="C1:C8"/>
+  <tableColumns count="1">
+    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fb20b906150&gt;"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblPlateformes" displayName="tblPlateformes" ref="E1:E4" headerRowCount="1">
+  <autoFilter ref="E1:E4"/>
+  <tableColumns count="1">
+    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fb20b905c70&gt;"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblInteractions" displayName="tblInteractions" ref="G1:G4" headerRowCount="1">
+  <autoFilter ref="G1:G4"/>
+  <tableColumns count="1">
+    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fb24deb7710&gt;"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -56957,7 +57007,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
@@ -57493,7 +57543,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -57953,16 +58003,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1">
-        <f t="array" ref="A:A">_xlfn.UNIQUE(DATA!B:B)</f>
+        <f t="array" ref="A1:A3">_xlfn.UNIQUE(DATA!B:B)</f>
         <v/>
       </c>
+      <c r="C1">
+        <f t="array" ref="C1:C8">_xlfn.UNIQUE(DATA!A:A)</f>
+        <v/>
+      </c>
+      <c r="E1">
+        <f t="array" ref="E1:E4">_xlfn.UNIQUE(DATA!D:D)</f>
+        <v/>
+      </c>
+      <c r="G1">
+        <f t="array" ref="G1:G4">_xlfn.UNIQUE(DATA!I:I)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="4">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Genre</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Âge</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Plateforme</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Interaction</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A10:B11"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="A4:B5"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="C1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=CALC!$A$2:$A$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="C1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=CALC!$A$2:$A$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=CALC!$C$2:$C$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=CALC!$E$2:$E$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=CALC!$G$2:$G$5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/template/Projet_ODD_SIVARAJAH.xlsx
+++ b/template/Projet_ODD_SIVARAJAH.xlsx
@@ -45,7 +45,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
         <bgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -168,6 +174,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -244,11 +254,176 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Niveau d'addiction (Filtré)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'TAB_CROISE_DYNAMIQUE'!A72</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$71:$H$71</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$72:$H$72</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'TAB_CROISE_DYNAMIQUE'!A73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$71:$H$71</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$73:$H$73</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="-10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Âge</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Niveau d'addiction</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblGenres" displayName="tblGenres" ref="A1:A3" headerRowCount="1">
   <autoFilter ref="A1:A3"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f3a1a89b830&gt;"/>
+    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c06c90&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -258,7 +433,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblAges" displayName="tblAges" ref="C1:C8" headerRowCount="1">
   <autoFilter ref="C1:C8"/>
   <tableColumns count="1">
-    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f3a1a89b710&gt;"/>
+    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c052b0&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -268,7 +443,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblPlateformes" displayName="tblPlateformes" ref="E1:E4" headerRowCount="1">
   <autoFilter ref="E1:E4"/>
   <tableColumns count="1">
-    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f3a1a89a750&gt;"/>
+    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c05730&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -278,7 +453,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblInteractions" displayName="tblInteractions" ref="G1:G4" headerRowCount="1">
   <autoFilter ref="G1:G4"/>
   <tableColumns count="1">
-    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f3a1a89bd70&gt;"/>
+    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c06990&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -58243,6 +58418,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -58312,7 +58488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -59101,8 +59277,114 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>ZONE DYNAMIQUE - Graphique 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="17">
+        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,1),"")</f>
+        <v/>
+      </c>
+      <c r="C71" s="17">
+        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,2),"")</f>
+        <v/>
+      </c>
+      <c r="D71" s="17">
+        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,3),"")</f>
+        <v/>
+      </c>
+      <c r="E71" s="17">
+        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,4),"")</f>
+        <v/>
+      </c>
+      <c r="F71" s="17">
+        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,5),"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="17">
+        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,6),"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="17">
+        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,7),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18">
+        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,1),"")</f>
+        <v/>
+      </c>
+      <c r="B72" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="C72" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="D72" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="E72" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="F72" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="G72" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="H72" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18">
+        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,2),"")</f>
+        <v/>
+      </c>
+      <c r="B73" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="C73" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="D73" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="E73" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="F73" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="G73" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+      <c r="H73" s="19">
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A70:H70"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A45:E45"/>

--- a/template/Projet_ODD_SIVARAJAH.xlsx
+++ b/template/Projet_ODD_SIVARAJAH.xlsx
@@ -13,8 +13,7 @@
     <sheet name="Correlations" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CALC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="TDB_1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TDB_2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TAB_CROISE_DYNAMIQUE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TAB_CROISE_DYNAMIQUE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,7 +144,7 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -174,7 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -267,7 +266,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Niveau d'addiction (Filtré)</a:t>
+              <a:t>Niveau d'addiction moyen selon l'âge et le genre</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -326,7 +325,7 @@
           </val>
         </ser>
         <gapWidth val="150"/>
-        <overlap val="-10"/>
+        <overlap val="-15"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -423,7 +422,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblGenres" displayName="tblGenres" ref="A1:A3" headerRowCount="1">
   <autoFilter ref="A1:A3"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c06c90&gt;"/>
+    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f57aaee6a50&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -433,7 +432,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblAges" displayName="tblAges" ref="C1:C8" headerRowCount="1">
   <autoFilter ref="C1:C8"/>
   <tableColumns count="1">
-    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c052b0&gt;"/>
+    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f58c28d5190&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -443,7 +442,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblPlateformes" displayName="tblPlateformes" ref="E1:E4" headerRowCount="1">
   <autoFilter ref="E1:E4"/>
   <tableColumns count="1">
-    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c05730&gt;"/>
+    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f58c28d50d0&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -453,7 +452,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblInteractions" displayName="tblInteractions" ref="G1:G4" headerRowCount="1">
   <autoFilter ref="G1:G4"/>
   <tableColumns count="1">
-    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f9259c06990&gt;"/>
+    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f58c28d6750&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -58322,8 +58321,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -58334,13 +58339,67 @@
       <c r="B1" s="3" t="n"/>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Tous</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="n"/>
       <c r="B2" s="6" t="n"/>
+      <c r="AA2">
+        <f>CALC!A2</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>CALC!C2</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>CALC!E2</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>CALC!G2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="AA3">
+        <f>CALC!A3</f>
+        <v/>
+      </c>
+      <c r="AB3">
+        <f>CALC!C3</f>
+        <v/>
+      </c>
+      <c r="AC3">
+        <f>CALC!E3</f>
+        <v/>
+      </c>
+      <c r="AD3">
+        <f>CALC!G3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -58351,13 +58410,35 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="AB4">
+        <f>CALC!C4</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>CALC!E4</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>CALC!G4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="6" t="n"/>
+      <c r="AB5">
+        <f>CALC!C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="AB6">
+        <f>CALC!C6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -58368,13 +58449,21 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Instagram</t>
-        </is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="AB7">
+        <f>CALC!C7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="6" t="n"/>
+      <c r="AB8">
+        <f>CALC!C8</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -58385,7 +58474,7 @@
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Tous</t>
         </is>
       </c>
     </row>
@@ -58400,21 +58489,18 @@
     <mergeCell ref="A7:B8"/>
     <mergeCell ref="A4:B5"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation sqref="C1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=CALC!$A$2:$A$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="C1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=CALC!$A$2:$A$4</formula1>
+      <formula1>=$AA$1:$AA$3</formula1>
     </dataValidation>
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=CALC!$C$2:$C$9</formula1>
+      <formula1>=$AB$1:$AB$8</formula1>
     </dataValidation>
     <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=CALC!$E$2:$E$5</formula1>
+      <formula1>=$AC$1:$AC$4</formula1>
     </dataValidation>
     <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=CALC!$G$2:$G$5</formula1>
+      <formula1>=$AD$1:$AD$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -58423,66 +58509,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="n"/>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="6" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Âge</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:B5"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="C1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=CALC!$A$2:$A$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=CALC!$C$2:$C$9</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -59286,99 +59312,99 @@
     </row>
     <row r="71">
       <c r="B71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,1),"")</f>
+        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,2),"")</f>
         <v/>
       </c>
       <c r="C71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,2),"")</f>
+        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,3),"")</f>
         <v/>
       </c>
       <c r="D71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,3),"")</f>
+        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,4),"")</f>
         <v/>
       </c>
       <c r="E71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,4),"")</f>
+        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,5),"")</f>
         <v/>
       </c>
       <c r="F71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,5),"")</f>
+        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,6),"")</f>
         <v/>
       </c>
       <c r="G71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,6),"")</f>
+        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,7),"")</f>
         <v/>
       </c>
       <c r="H71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,7),"")</f>
+        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,8),"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="18">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,1),"")</f>
+        <f>IFERROR(INDEX(CALC!$A$1:$A$1000,2),"")</f>
         <v/>
       </c>
       <c r="B72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="C72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="D72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="E72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="F72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="G72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="H72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A72, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="18">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,2),"")</f>
+        <f>IFERROR(INDEX(CALC!$A$1:$A$1000,3),"")</f>
         <v/>
       </c>
       <c r="B73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="C73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="D73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="E73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="F73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="G73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="H73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A73, DATA!$B:$B, TDB_1!$C$1, DATA!$A:$A, TDB_1!$C$4, DATA!$D:$D, TDB_1!$C$7, DATA!$I:$I, TDB_1!$C$10), NA())</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>

--- a/template/Projet_ODD_SIVARAJAH.xlsx
+++ b/template/Projet_ODD_SIVARAJAH.xlsx
@@ -44,7 +44,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,12 +73,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
         <bgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,10 +167,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -281,7 +271,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!A72</f>
+              <f>'TAB_CROISE_DYNAMIQUE'!A12</f>
             </strRef>
           </tx>
           <spPr>
@@ -291,12 +281,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$71:$H$71</f>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$11:$H$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$72:$H$72</f>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$12:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -305,7 +295,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!A73</f>
+              <f>'TAB_CROISE_DYNAMIQUE'!A13</f>
             </strRef>
           </tx>
           <spPr>
@@ -315,12 +305,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$71:$H$71</f>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$11:$H$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$73:$H$73</f>
+              <f>'TAB_CROISE_DYNAMIQUE'!$B$13:$H$13</f>
             </numRef>
           </val>
         </ser>
@@ -395,9 +385,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -422,7 +412,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblGenres" displayName="tblGenres" ref="A1:A3" headerRowCount="1">
   <autoFilter ref="A1:A3"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f57aaee6a50&gt;"/>
+    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f57abe77ad0&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -432,7 +422,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblAges" displayName="tblAges" ref="C1:C8" headerRowCount="1">
   <autoFilter ref="C1:C8"/>
   <tableColumns count="1">
-    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f58c28d5190&gt;"/>
+    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f57ac3c9970&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -442,7 +432,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblPlateformes" displayName="tblPlateformes" ref="E1:E4" headerRowCount="1">
   <autoFilter ref="E1:E4"/>
   <tableColumns count="1">
-    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f58c28d50d0&gt;"/>
+    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f57ac3c8230&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -452,7 +442,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblInteractions" displayName="tblInteractions" ref="G1:G4" headerRowCount="1">
   <autoFilter ref="G1:G4"/>
   <tableColumns count="1">
-    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f58c28d6750&gt;"/>
+    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f57ac3c9af0&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -58514,7 +58504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -58539,7 +58529,7 @@
         </is>
       </c>
       <c r="L1">
-        <f t="array" ref="L1">INDEX(DATA!$D$2:$D$1201, MATCH(MAX(COUNTIFS(DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, "&lt;&gt;Both")), COUNTIFS(DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, "&lt;&gt;Both"), 0))</f>
+        <f t="array" ref="L1">INDEX(DATA!$D$2:$D$1201, MATCH(MAX(COUNTIFS(DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, "&lt;&gt;Both", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))), COUNTIFS(DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, "&lt;&gt;Both", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), 0))</f>
         <v/>
       </c>
     </row>
@@ -58583,7 +58573,7 @@
         </is>
       </c>
       <c r="L2">
-        <f>AVERAGEIF(DATA!M:M, 1, DATA!G:G)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!G:G, DATA!M:M, 1, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -58593,31 +58583,31 @@
         <v/>
       </c>
       <c r="B3" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$B$2,DATA!$B:$B,$A3),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$B$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="C3" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$C$2,DATA!$B:$B,$A3),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$C$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="D3" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$D$2,DATA!$B:$B,$A3),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$D$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="E3" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$E$2,DATA!$B:$B,$A3),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$E$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="F3" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$F$2,DATA!$B:$B,$A3),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$F$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="G3" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$G$2,DATA!$B:$B,$A3),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$G$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="H3" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$H$2,DATA!$B:$B,$A3),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$H$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
     </row>
@@ -58627,31 +58617,31 @@
         <v/>
       </c>
       <c r="B4" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$B$2,DATA!$B:$B,$A4),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$B$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$C$2,DATA!$B:$B,$A4),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$C$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$D$2,DATA!$B:$B,$A4),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$D$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$E$2,DATA!$B:$B,$A4),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$E$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="F4" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$F$2,DATA!$B:$B,$A4),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$F$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="G4" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$G$2,DATA!$B:$B,$A4),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$G$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
       <c r="H4" s="10">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$H$2,DATA!$B:$B,$A4),0)</f>
+        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$H$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
         <v/>
       </c>
     </row>
@@ -58703,31 +58693,31 @@
         <v/>
       </c>
       <c r="B12" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$B$11,DATA!$B:$B,$A12),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$B$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="C12" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$C$11,DATA!$B:$B,$A12),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$C$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="D12" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$D$11,DATA!$B:$B,$A12),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$D$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="E12" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$E$11,DATA!$B:$B,$A12),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$E$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="F12" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$F$11,DATA!$B:$B,$A12),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$F$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="G12" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$G$11,DATA!$B:$B,$A12),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$G$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="H12" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$H$11,DATA!$B:$B,$A12),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$H$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
     </row>
@@ -58737,31 +58727,31 @@
         <v/>
       </c>
       <c r="B13" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$B$11,DATA!$B:$B,$A13),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$B$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$C$11,DATA!$B:$B,$A13),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$C$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$D$11,DATA!$B:$B,$A13),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$D$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="E13" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$E$11,DATA!$B:$B,$A13),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$E$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="F13" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$F$11,DATA!$B:$B,$A13),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$F$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="G13" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$G$11,DATA!$B:$B,$A13),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$G$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
       <c r="H13" s="11">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$H$11,DATA!$B:$B,$A13),0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$H$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
         <v/>
       </c>
     </row>
@@ -58815,27 +58805,27 @@
         <v/>
       </c>
       <c r="B18" s="14">
-        <f t="array" ref="B18">MIN(IF(DATA!$A$2:$A$1201=$A18, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="B18">MIN(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f t="array" ref="C18">QUARTILE(IF(DATA!$A$2:$A$1201=$A18, DATA!$L$2:$L$1201), 1)</f>
+        <f t="array" ref="C18">QUARTILE(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
         <v/>
       </c>
       <c r="D18" s="14">
-        <f t="array" ref="D18">MEDIAN(IF(DATA!$A$2:$A$1201=$A18, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="D18">MEDIAN(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="E18" s="14">
-        <f t="array" ref="E18">QUARTILE(IF(DATA!$A$2:$A$1201=$A18, DATA!$L$2:$L$1201), 3)</f>
+        <f t="array" ref="E18">QUARTILE(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
         <v/>
       </c>
       <c r="F18" s="14">
-        <f t="array" ref="F18">MAX(IF(DATA!$A$2:$A$1201=$A18, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="F18">MAX(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="G18" s="14">
-        <f>AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A18)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A18, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -58845,27 +58835,27 @@
         <v/>
       </c>
       <c r="B19" s="14">
-        <f t="array" ref="B19">MIN(IF(DATA!$A$2:$A$1201=$A19, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="B19">MIN(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="C19" s="14">
-        <f t="array" ref="C19">QUARTILE(IF(DATA!$A$2:$A$1201=$A19, DATA!$L$2:$L$1201), 1)</f>
+        <f t="array" ref="C19">QUARTILE(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
         <v/>
       </c>
       <c r="D19" s="14">
-        <f t="array" ref="D19">MEDIAN(IF(DATA!$A$2:$A$1201=$A19, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="D19">MEDIAN(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="E19" s="14">
-        <f t="array" ref="E19">QUARTILE(IF(DATA!$A$2:$A$1201=$A19, DATA!$L$2:$L$1201), 3)</f>
+        <f t="array" ref="E19">QUARTILE(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
         <v/>
       </c>
       <c r="F19" s="14">
-        <f t="array" ref="F19">MAX(IF(DATA!$A$2:$A$1201=$A19, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="F19">MAX(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="G19" s="14">
-        <f>AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A19)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A19, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -58875,27 +58865,27 @@
         <v/>
       </c>
       <c r="B20" s="14">
-        <f t="array" ref="B20">MIN(IF(DATA!$A$2:$A$1201=$A20, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="B20">MIN(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f t="array" ref="C20">QUARTILE(IF(DATA!$A$2:$A$1201=$A20, DATA!$L$2:$L$1201), 1)</f>
+        <f t="array" ref="C20">QUARTILE(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f t="array" ref="D20">MEDIAN(IF(DATA!$A$2:$A$1201=$A20, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="D20">MEDIAN(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f t="array" ref="E20">QUARTILE(IF(DATA!$A$2:$A$1201=$A20, DATA!$L$2:$L$1201), 3)</f>
+        <f t="array" ref="E20">QUARTILE(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f t="array" ref="F20">MAX(IF(DATA!$A$2:$A$1201=$A20, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="F20">MAX(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A20)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A20, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -58905,27 +58895,27 @@
         <v/>
       </c>
       <c r="B21" s="14">
-        <f t="array" ref="B21">MIN(IF(DATA!$A$2:$A$1201=$A21, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="B21">MIN(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f t="array" ref="C21">QUARTILE(IF(DATA!$A$2:$A$1201=$A21, DATA!$L$2:$L$1201), 1)</f>
+        <f t="array" ref="C21">QUARTILE(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
         <v/>
       </c>
       <c r="D21" s="14">
-        <f t="array" ref="D21">MEDIAN(IF(DATA!$A$2:$A$1201=$A21, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="D21">MEDIAN(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="E21" s="14">
-        <f t="array" ref="E21">QUARTILE(IF(DATA!$A$2:$A$1201=$A21, DATA!$L$2:$L$1201), 3)</f>
+        <f t="array" ref="E21">QUARTILE(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
         <v/>
       </c>
       <c r="F21" s="14">
-        <f t="array" ref="F21">MAX(IF(DATA!$A$2:$A$1201=$A21, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="F21">MAX(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="G21" s="14">
-        <f>AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A21)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A21, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -58935,27 +58925,27 @@
         <v/>
       </c>
       <c r="B22" s="14">
-        <f t="array" ref="B22">MIN(IF(DATA!$A$2:$A$1201=$A22, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="B22">MIN(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="C22" s="14">
-        <f t="array" ref="C22">QUARTILE(IF(DATA!$A$2:$A$1201=$A22, DATA!$L$2:$L$1201), 1)</f>
+        <f t="array" ref="C22">QUARTILE(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f t="array" ref="D22">MEDIAN(IF(DATA!$A$2:$A$1201=$A22, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="D22">MEDIAN(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="E22" s="14">
-        <f t="array" ref="E22">QUARTILE(IF(DATA!$A$2:$A$1201=$A22, DATA!$L$2:$L$1201), 3)</f>
+        <f t="array" ref="E22">QUARTILE(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
         <v/>
       </c>
       <c r="F22" s="14">
-        <f t="array" ref="F22">MAX(IF(DATA!$A$2:$A$1201=$A22, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="F22">MAX(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="G22" s="14">
-        <f>AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A22)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A22, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -58965,27 +58955,27 @@
         <v/>
       </c>
       <c r="B23" s="14">
-        <f t="array" ref="B23">MIN(IF(DATA!$A$2:$A$1201=$A23, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="B23">MIN(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="C23" s="14">
-        <f t="array" ref="C23">QUARTILE(IF(DATA!$A$2:$A$1201=$A23, DATA!$L$2:$L$1201), 1)</f>
+        <f t="array" ref="C23">QUARTILE(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
         <v/>
       </c>
       <c r="D23" s="14">
-        <f t="array" ref="D23">MEDIAN(IF(DATA!$A$2:$A$1201=$A23, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="D23">MEDIAN(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="E23" s="14">
-        <f t="array" ref="E23">QUARTILE(IF(DATA!$A$2:$A$1201=$A23, DATA!$L$2:$L$1201), 3)</f>
+        <f t="array" ref="E23">QUARTILE(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
         <v/>
       </c>
       <c r="F23" s="14">
-        <f t="array" ref="F23">MAX(IF(DATA!$A$2:$A$1201=$A23, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="F23">MAX(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="G23" s="14">
-        <f>AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A23)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A23, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -58995,27 +58985,27 @@
         <v/>
       </c>
       <c r="B24" s="14">
-        <f t="array" ref="B24">MIN(IF(DATA!$A$2:$A$1201=$A24, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="B24">MIN(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="C24" s="14">
-        <f t="array" ref="C24">QUARTILE(IF(DATA!$A$2:$A$1201=$A24, DATA!$L$2:$L$1201), 1)</f>
+        <f t="array" ref="C24">QUARTILE(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
         <v/>
       </c>
       <c r="D24" s="14">
-        <f t="array" ref="D24">MEDIAN(IF(DATA!$A$2:$A$1201=$A24, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="D24">MEDIAN(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="E24" s="14">
-        <f t="array" ref="E24">QUARTILE(IF(DATA!$A$2:$A$1201=$A24, DATA!$L$2:$L$1201), 3)</f>
+        <f t="array" ref="E24">QUARTILE(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
         <v/>
       </c>
       <c r="F24" s="14">
-        <f t="array" ref="F24">MAX(IF(DATA!$A$2:$A$1201=$A24, DATA!$L$2:$L$1201))</f>
+        <f t="array" ref="F24">MAX(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
         <v/>
       </c>
       <c r="G24" s="14">
-        <f>AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A24)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A24, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -59044,7 +59034,7 @@
         <v/>
       </c>
       <c r="B32" s="15">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A32, DATA!$M$2:$M$1201, 1)</f>
+        <f>COUNTIFS(DATA!$A$2:$A$1201, $A32, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
         <v/>
       </c>
     </row>
@@ -59054,7 +59044,7 @@
         <v/>
       </c>
       <c r="B33" s="15">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A33, DATA!$M$2:$M$1201, 1)</f>
+        <f>COUNTIFS(DATA!$A$2:$A$1201, $A33, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
         <v/>
       </c>
     </row>
@@ -59064,7 +59054,7 @@
         <v/>
       </c>
       <c r="B34" s="15">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A34, DATA!$M$2:$M$1201, 1)</f>
+        <f>COUNTIFS(DATA!$A$2:$A$1201, $A34, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
         <v/>
       </c>
     </row>
@@ -59074,7 +59064,7 @@
         <v/>
       </c>
       <c r="B35" s="15">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A35, DATA!$M$2:$M$1201, 1)</f>
+        <f>COUNTIFS(DATA!$A$2:$A$1201, $A35, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
         <v/>
       </c>
     </row>
@@ -59084,7 +59074,7 @@
         <v/>
       </c>
       <c r="B36" s="15">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A36, DATA!$M$2:$M$1201, 1)</f>
+        <f>COUNTIFS(DATA!$A$2:$A$1201, $A36, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
         <v/>
       </c>
     </row>
@@ -59094,7 +59084,7 @@
         <v/>
       </c>
       <c r="B37" s="15">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A37, DATA!$M$2:$M$1201, 1)</f>
+        <f>COUNTIFS(DATA!$A$2:$A$1201, $A37, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
         <v/>
       </c>
     </row>
@@ -59104,7 +59094,7 @@
         <v/>
       </c>
       <c r="B38" s="15">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A38, DATA!$M$2:$M$1201, 1)</f>
+        <f>COUNTIFS(DATA!$A$2:$A$1201, $A38, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
         <v/>
       </c>
     </row>
@@ -59148,19 +59138,19 @@
         <v/>
       </c>
       <c r="B47" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&lt;2"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&lt;2", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="C47" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=2", DATA!$C$2:$C$1201, "&lt;4"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=2", DATA!$C$2:$C$1201, "&lt;4", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="D47" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=4", DATA!$C$2:$C$1201, "&lt;6"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=4", DATA!$C$2:$C$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="E47" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=6"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -59170,19 +59160,19 @@
         <v/>
       </c>
       <c r="B48" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&lt;2"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&lt;2", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="C48" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=2", DATA!$C$2:$C$1201, "&lt;4"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=2", DATA!$C$2:$C$1201, "&lt;4", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="D48" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=4", DATA!$C$2:$C$1201, "&lt;6"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=4", DATA!$C$2:$C$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="E48" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=6"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -59231,23 +59221,23 @@
         <v/>
       </c>
       <c r="B57" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&lt;5"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&lt;5", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="C57" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="D57" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="E57" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="F57" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=8"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -59257,23 +59247,23 @@
         <v/>
       </c>
       <c r="B58" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&lt;5"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&lt;5", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="C58" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="D58" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="E58" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="F58" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=8"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
@@ -59283,134 +59273,28 @@
         <v/>
       </c>
       <c r="B59" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&lt;5"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&lt;5", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="C59" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="D59" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="E59" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
       <c r="F59" s="14">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=8"), 0)</f>
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>ZONE DYNAMIQUE - Graphique 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="C71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,3),"")</f>
-        <v/>
-      </c>
-      <c r="D71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,4),"")</f>
-        <v/>
-      </c>
-      <c r="E71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,5),"")</f>
-        <v/>
-      </c>
-      <c r="F71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,6),"")</f>
-        <v/>
-      </c>
-      <c r="G71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,7),"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="17">
-        <f>IFERROR(INDEX(CALC!$C$1:$C$1000,8),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="18">
-        <f>IFERROR(INDEX(CALC!$A$1:$A$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="B72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="C72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="D72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="E72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="F72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="G72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="H72" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A72, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="18">
-        <f>IFERROR(INDEX(CALC!$A$1:$A$1000,3),"")</f>
-        <v/>
-      </c>
-      <c r="B73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $B$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="C73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $C$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="D73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $D$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="E73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $E$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="F73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $F$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="G73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $G$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="H73" s="19">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L, DATA!$A:$A, $H$71, DATA!$B:$B, $A73, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A70:H70"/>
+  <mergeCells count="6">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A45:E45"/>

--- a/template/Projet_ODD_SIVARAJAH.xlsx
+++ b/template/Projet_ODD_SIVARAJAH.xlsx
@@ -8,12 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indicateurs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="TCD" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Correlations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CALC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TDB_1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TAB_CROISE_DYNAMIQUE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,68 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00333333"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00595959"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00D97706"/>
-      <sz val="16"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C0C0C0"/>
-        <bgColor rgb="00C0C0C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-        <bgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -100,121 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00A6A6A6"/>
-      </left>
-      <right style="thin">
-        <color rgb="00A6A6A6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00A6A6A6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00A6A6A6"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -289,561 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Niveau d'addiction moyen selon l'âge et le genre</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!A12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$11:$H$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$12:$H$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!A13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$11:$H$11</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$13:$H$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="-15"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Âge</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Niveau d'addiction</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Répartition de la dépression selon le genre</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!B101</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$A$102:$A$103</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$102:$B$103</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showVal val="0"/>
-          <showPercent val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Répartition niveau Addiction selon l'âge</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <stockChart>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!B17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$A$18:$A$24</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$B$18:$B$24</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!C17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$A$18:$A$24</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$C$18:$C$24</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!D17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$A$18:$A$24</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$D$18:$D$24</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!E17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$A$18:$A$24</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$E$18:$E$24</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!F17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$A$18:$A$24</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'TAB_CROISE_DYNAMIQUE'!$F$18:$F$24</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </stockChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Âge</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Niveau d'addiction</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>14</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5760000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblGenres" displayName="tblGenres" ref="A1:A3" headerRowCount="1">
-  <autoFilter ref="A1:A3"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f61f3486cf0&gt;"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblAges" displayName="tblAges" ref="C1:C8" headerRowCount="1">
-  <autoFilter ref="C1:C8"/>
-  <tableColumns count="1">
-    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f61f3518f50&gt;"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblPlateformes" displayName="tblPlateformes" ref="E1:E4" headerRowCount="1">
-  <autoFilter ref="E1:E4"/>
-  <tableColumns count="1">
-    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f61f3518b90&gt;"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblInteractions" displayName="tblInteractions" ref="G1:G4" headerRowCount="1">
-  <autoFilter ref="G1:G4"/>
-  <tableColumns count="1">
-    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7f61f3734b00&gt;"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57608,2196 +56886,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Nombre de filles dépressives</t>
-        </is>
-      </c>
-      <c r="B1">
-        <f>COUNTIFS(DATA!M:M,1,DATA!B:B,"female")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Nombre de garçons dépressifs</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>COUNTIFS(DATA!M:M,1,DATA!B:B,"male")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Niveau d'addiction moyen chez les filles</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>AVERAGEIF(DATA!B:B,"female",DATA!L:L)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Niveau d'addiction moyen chez les garçons</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>AVERAGEIF(DATA!B:B,"male",DATA!L:L)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Niveau de dépression selon l'âge</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nb depressifs</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>16</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Niveau d'addiction moyen selon l'âge et le genre</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Addiction moy. Filles</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Addiction moy. Garcons</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4.96</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5.53</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="C18" t="n">
-        <v>5.62</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="C19" t="n">
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="C20" t="n">
-        <v>5.97</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>5.68</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Nombre de dépressions selon le temps de sommeil et l'interaction sociale</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Interaction sociale/Temps de Sommeil</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>&lt;5h</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>5-6h</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6-7h</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>7-8h</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>&gt;8h</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>7</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>6</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Répartition du niveau d'addiction selon l'âge</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Mediane</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Moyenne</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>IQR</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>13</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" t="n">
-        <v>6</v>
-      </c>
-      <c r="D35" t="n">
-        <v>8</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="n">
-        <v>10</v>
-      </c>
-      <c r="G35" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="H35" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>14</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D36" t="n">
-        <v>8</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>10</v>
-      </c>
-      <c r="G36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H36" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>15</v>
-      </c>
-      <c r="B37" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" t="n">
-        <v>5</v>
-      </c>
-      <c r="D37" t="n">
-        <v>7</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
-        <v>10</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>16</v>
-      </c>
-      <c r="B38" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" t="n">
-        <v>8</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>10</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="H38" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>17</v>
-      </c>
-      <c r="B39" t="n">
-        <v>3</v>
-      </c>
-      <c r="C39" t="n">
-        <v>6</v>
-      </c>
-      <c r="D39" t="n">
-        <v>8</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10</v>
-      </c>
-      <c r="G39" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="H39" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>18</v>
-      </c>
-      <c r="B40" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>8</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>10</v>
-      </c>
-      <c r="G40" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="H40" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>19</v>
-      </c>
-      <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" t="n">
-        <v>6</v>
-      </c>
-      <c r="D41" t="n">
-        <v>8</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>10</v>
-      </c>
-      <c r="G41" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="H41" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Matrice de corrélation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Variable</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sleep_hours</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>daily_social_media_hours</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>academic_performance</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>physical_activity</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>social_num</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>stress_level</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>anxiety_level</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>addiction_level</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>depression_label</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sleep_hours</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>daily_social_media_hours</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>academic_performance</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>physical_activity</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>social_num</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>stress_level</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>anxiety_level</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>addiction_level</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>depression_label</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f t="array" ref="A1:A3">_xlfn.UNIQUE(DATA!B:B)</f>
-        <v/>
-      </c>
-      <c r="C1">
-        <f t="array" ref="C1:C8">_xlfn.UNIQUE(DATA!A:A)</f>
-        <v/>
-      </c>
-      <c r="E1">
-        <f t="array" ref="E1:E4">_xlfn.UNIQUE(DATA!D:D)</f>
-        <v/>
-      </c>
-      <c r="G1">
-        <f t="array" ref="G1:G4">_xlfn.UNIQUE(DATA!I:I)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="4">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
-    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
-    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
-    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="n"/>
-      <c r="B2" s="7" t="n"/>
-      <c r="AA2">
-        <f>CALC!A2</f>
-        <v/>
-      </c>
-      <c r="AB2">
-        <f>CALC!C2</f>
-        <v/>
-      </c>
-      <c r="AC2">
-        <f>CALC!E2</f>
-        <v/>
-      </c>
-      <c r="AD2">
-        <f>CALC!G2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="AA3">
-        <f>CALC!A3</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>CALC!C3</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>CALC!E3</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>CALC!G3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Âge</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-      <c r="AB4">
-        <f>CALC!C4</f>
-        <v/>
-      </c>
-      <c r="AC4">
-        <f>CALC!E4</f>
-        <v/>
-      </c>
-      <c r="AD4">
-        <f>CALC!G4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="AB5">
-        <f>CALC!C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="AB6">
-        <f>CALC!C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Plateforme</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-      <c r="AB7">
-        <f>CALC!C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="AB8">
-        <f>CALC!C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Interaction</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Tous</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="T20" s="18" t="inlineStr">
-        <is>
-          <t>Réseau le plus utilisé</t>
-        </is>
-      </c>
-      <c r="U20" s="19" t="n"/>
-      <c r="V20" s="19" t="n"/>
-    </row>
-    <row r="21">
-      <c r="T21" s="19" t="n"/>
-      <c r="U21" s="19" t="n"/>
-      <c r="V21" s="19" t="n"/>
-    </row>
-    <row r="22">
-      <c r="T22" s="20">
-        <f>'TAB_CROISE_DYNAMIQUE'!L1</f>
-        <v/>
-      </c>
-      <c r="U22" s="19" t="n"/>
-      <c r="V22" s="19" t="n"/>
-    </row>
-    <row r="23">
-      <c r="T23" s="19" t="n"/>
-      <c r="U23" s="19" t="n"/>
-      <c r="V23" s="19" t="n"/>
-    </row>
-    <row r="25">
-      <c r="T25" s="18" t="inlineStr">
-        <is>
-          <t>Performance scolaire
-Moyen des personnes dépressives</t>
-        </is>
-      </c>
-      <c r="U25" s="19" t="n"/>
-      <c r="V25" s="19" t="n"/>
-    </row>
-    <row r="26">
-      <c r="T26" s="19" t="n"/>
-      <c r="U26" s="19" t="n"/>
-      <c r="V26" s="19" t="n"/>
-    </row>
-    <row r="27">
-      <c r="T27" s="21">
-        <f>'TAB_CROISE_DYNAMIQUE'!L2</f>
-        <v/>
-      </c>
-      <c r="U27" s="19" t="n"/>
-      <c r="V27" s="19" t="n"/>
-    </row>
-    <row r="28">
-      <c r="T28" s="19" t="n"/>
-      <c r="U28" s="19" t="n"/>
-      <c r="V28" s="19" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="T20:V21"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="T27:V28"/>
-    <mergeCell ref="A10:B11"/>
-    <mergeCell ref="T22:V23"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="T25:V26"/>
-  </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="C1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=$AA$1:$AA$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=$AB$1:$AB$8</formula1>
-    </dataValidation>
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=$AC$1:$AC$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=$AD$1:$AD$4</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L103"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Dépression par Âge et Genre</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Réseau le plus utilisé</t>
-        </is>
-      </c>
-      <c r="L1">
-        <f t="array" ref="L1">INDEX(DATA!$D$2:$D$1201, MATCH(MAX(COUNTIFS(DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, "&lt;&gt;Both", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))), COUNTIFS(DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, DATA!$D$2:$D$1201, "&lt;&gt;Both", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), 0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="B2" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="C2" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="D2" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,3),"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,4),"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,5),"")</f>
-        <v/>
-      </c>
-      <c r="G2" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,6),"")</f>
-        <v/>
-      </c>
-      <c r="H2" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,7),"")</f>
-        <v/>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Perf sco moyenne - dépressifs</t>
-        </is>
-      </c>
-      <c r="L2">
-        <f>IFERROR(AVERAGEIFS(DATA!G:G, DATA!M:M, 1, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="B3" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$B$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="C3" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$C$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="D3" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$D$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="E3" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$E$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="F3" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$F$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="G3" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$G$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="H3" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$H$2,DATA!$B:$B,$A3, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="B4" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$B$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$C$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$D$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$E$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$F$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$G$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="11">
-        <f>IFERROR(COUNTIFS(DATA!$M:$M,1,DATA!$A:$A,$H$2,DATA!$B:$B,$A4, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Addiction moyenne par Âge et Genre</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="B11" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="C11" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,3),"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,4),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,5),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,6),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="9">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,7),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="B12" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$B$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="C12" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$C$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="D12" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$D$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="E12" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$E$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="F12" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$F$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="G12" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$G$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="H12" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$H$11,DATA!$B:$B,$A12, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="B13" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$B$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="C13" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$C$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="D13" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$D$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="E13" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$E$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$F$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="G13" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$G$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-      <c r="H13" s="12">
-        <f>IFERROR(AVERAGEIFS(DATA!$L:$L,DATA!$A:$A,$H$11,DATA!$B:$B,$A13, DATA!$B:$B, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A:$A, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D:$D, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I:$I, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)),NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Répartition de l'addiction selon l'âge</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Âge</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Médiane</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>Moyenne</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="B18" s="15">
-        <f t="array" ref="B18">MIN(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="C18" s="15">
-        <f t="array" ref="C18">QUARTILE(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
-        <v/>
-      </c>
-      <c r="D18" s="15">
-        <f t="array" ref="D18">MEDIAN(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="E18" s="15">
-        <f t="array" ref="E18">QUARTILE(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
-        <v/>
-      </c>
-      <c r="F18" s="15">
-        <f t="array" ref="F18">MAX(IF((DATA!$A$2:$A$1201=$A18) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="G18" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A18, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="B19" s="15">
-        <f t="array" ref="B19">MIN(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="C19" s="15">
-        <f t="array" ref="C19">QUARTILE(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
-        <v/>
-      </c>
-      <c r="D19" s="15">
-        <f t="array" ref="D19">MEDIAN(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="E19" s="15">
-        <f t="array" ref="E19">QUARTILE(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
-        <v/>
-      </c>
-      <c r="F19" s="15">
-        <f t="array" ref="F19">MAX(IF((DATA!$A$2:$A$1201=$A19) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="G19" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A19, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,3),"")</f>
-        <v/>
-      </c>
-      <c r="B20" s="15">
-        <f t="array" ref="B20">MIN(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="C20" s="15">
-        <f t="array" ref="C20">QUARTILE(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
-        <v/>
-      </c>
-      <c r="D20" s="15">
-        <f t="array" ref="D20">MEDIAN(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="E20" s="15">
-        <f t="array" ref="E20">QUARTILE(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
-        <v/>
-      </c>
-      <c r="F20" s="15">
-        <f t="array" ref="F20">MAX(IF((DATA!$A$2:$A$1201=$A20) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="G20" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A20, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,4),"")</f>
-        <v/>
-      </c>
-      <c r="B21" s="15">
-        <f t="array" ref="B21">MIN(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="C21" s="15">
-        <f t="array" ref="C21">QUARTILE(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
-        <v/>
-      </c>
-      <c r="D21" s="15">
-        <f t="array" ref="D21">MEDIAN(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="E21" s="15">
-        <f t="array" ref="E21">QUARTILE(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
-        <v/>
-      </c>
-      <c r="F21" s="15">
-        <f t="array" ref="F21">MAX(IF((DATA!$A$2:$A$1201=$A21) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="G21" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A21, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,5),"")</f>
-        <v/>
-      </c>
-      <c r="B22" s="15">
-        <f t="array" ref="B22">MIN(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="C22" s="15">
-        <f t="array" ref="C22">QUARTILE(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
-        <f t="array" ref="D22">MEDIAN(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="E22" s="15">
-        <f t="array" ref="E22">QUARTILE(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
-        <v/>
-      </c>
-      <c r="F22" s="15">
-        <f t="array" ref="F22">MAX(IF((DATA!$A$2:$A$1201=$A22) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="G22" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A22, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,6),"")</f>
-        <v/>
-      </c>
-      <c r="B23" s="15">
-        <f t="array" ref="B23">MIN(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="C23" s="15">
-        <f t="array" ref="C23">QUARTILE(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
-        <v/>
-      </c>
-      <c r="D23" s="15">
-        <f t="array" ref="D23">MEDIAN(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="E23" s="15">
-        <f t="array" ref="E23">QUARTILE(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
-        <v/>
-      </c>
-      <c r="F23" s="15">
-        <f t="array" ref="F23">MAX(IF((DATA!$A$2:$A$1201=$A23) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="G23" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A23, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,7),"")</f>
-        <v/>
-      </c>
-      <c r="B24" s="15">
-        <f t="array" ref="B24">MIN(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="C24" s="15">
-        <f t="array" ref="C24">QUARTILE(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 1)</f>
-        <v/>
-      </c>
-      <c r="D24" s="15">
-        <f t="array" ref="D24">MEDIAN(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="E24" s="15">
-        <f t="array" ref="E24">QUARTILE(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201), 3)</f>
-        <v/>
-      </c>
-      <c r="F24" s="15">
-        <f t="array" ref="F24">MAX(IF((DATA!$A$2:$A$1201=$A24) * IF(TDB_1!$C$1="Tous", 1, DATA!$B$2:$B$1201=TDB_1!$C$1) * IF(TDB_1!$C$4="Tous", 1, DATA!$A$2:$A$1201=TDB_1!$C$4) * IF(TDB_1!$C$7="Tous", 1, DATA!$D$2:$D$1201=TDB_1!$C$7) * IF(TDB_1!$C$10="Tous", 1, DATA!$I$2:$I$1201=TDB_1!$C$10), DATA!$L$2:$L$1201))</f>
-        <v/>
-      </c>
-      <c r="G24" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$A$2:$A$1201, $A24, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Nombre de dépressions selon l'âge</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Âge</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Nb Dépressions</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="B32" s="16">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A32, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="B33" s="16">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A33, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,3),"")</f>
-        <v/>
-      </c>
-      <c r="B34" s="16">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A34, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,4),"")</f>
-        <v/>
-      </c>
-      <c r="B35" s="16">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A35, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,5),"")</f>
-        <v/>
-      </c>
-      <c r="B36" s="16">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A36, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,6),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="16">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A37, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14">
-        <f>IFERROR(INDEX(CALC!$C$2:$C$1000,7),"")</f>
-        <v/>
-      </c>
-      <c r="B38" s="16">
-        <f>COUNTIFS(DATA!$A$2:$A$1201, $A38, DATA!$M$2:$M$1201, 1, DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Performance scolaire selon Genre et Temps d'écran (Réseaux Sociaux)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 2h</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>2 à 4h</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>4 à 6h</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>&gt; 6h</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="B47" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&lt;2", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="C47" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=2", DATA!$C$2:$C$1201, "&lt;4", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="D47" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=4", DATA!$C$2:$C$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="E47" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A47, DATA!$C$2:$C$1201, "&gt;=6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10">
-        <f>IFERROR(INDEX(CALC!$A$2:$A$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="B48" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&lt;2", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="C48" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=2", DATA!$C$2:$C$1201, "&lt;4", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="D48" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=4", DATA!$C$2:$C$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="E48" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$B$2:$B$1201, $A48, DATA!$C$2:$C$1201, "&gt;=6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Anxiété moyenne par Interaction sociale et Temps de sommeil</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>Interaction</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 5h</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>5 à 6h</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>6 à 7h</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>7 à 8h</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="inlineStr">
-        <is>
-          <t>&gt; 8h</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10">
-        <f>IFERROR(INDEX(CALC!$G$2:$G$1000,1),"")</f>
-        <v/>
-      </c>
-      <c r="B57" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&lt;5", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="C57" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="D57" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="E57" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="F57" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A57, DATA!$E$2:$E$1201, "&gt;=8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10">
-        <f>IFERROR(INDEX(CALC!$G$2:$G$1000,2),"")</f>
-        <v/>
-      </c>
-      <c r="B58" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&lt;5", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="C58" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="D58" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="E58" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="F58" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A58, DATA!$E$2:$E$1201, "&gt;=8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10">
-        <f>IFERROR(INDEX(CALC!$G$2:$G$1000,3),"")</f>
-        <v/>
-      </c>
-      <c r="B59" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&lt;5", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="C59" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=5", DATA!$E$2:$E$1201, "&lt;6", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="D59" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=6", DATA!$E$2:$E$1201, "&lt;7", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="E59" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=7", DATA!$E$2:$E$1201, "&lt;8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-      <c r="F59" s="15">
-        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$I$2:$I$1201, $A59, DATA!$E$2:$E$1201, "&gt;=8", DATA!$B$2:$B$1201, IF(TDB_1!$C$1="Tous", "&lt;&gt;", TDB_1!$C$1), DATA!$A$2:$A$1201, IF(TDB_1!$C$4="Tous", "&lt;&gt;", TDB_1!$C$4), DATA!$D$2:$D$1201, IF(TDB_1!$C$7="Tous", "&lt;&gt;", TDB_1!$C$7), DATA!$I$2:$I$1201, IF(TDB_1!$C$10="Tous", "&lt;&gt;", TDB_1!$C$10)), NA())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="17" t="inlineStr">
-        <is>
-          <t>Total Dépression par Genre</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102">
-        <f>A3</f>
-        <v/>
-      </c>
-      <c r="B102">
-        <f>SUM(B3:H3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103">
-        <f>A4</f>
-        <v/>
-      </c>
-      <c r="B103">
-        <f>SUM(B4:H4)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A55:F55"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/template/Projet_ODD_SIVARAJAH.xlsx
+++ b/template/Projet_ODD_SIVARAJAH.xlsx
@@ -10,10 +10,13 @@
     <sheet name="TDB1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="TDB2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DATA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Correlations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CALC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TCD" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TCD2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TDB4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Correlations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CALC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TCD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TCD2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TCD3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TDB3" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -134,7 +137,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -176,11 +179,25 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -267,7 +284,23 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -841,7 +874,6 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1092,7 +1124,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Relation Sommeil / Dépression</a:t>
+              <a:t>Sommeil vs Addiction par Interaction Sociale</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1104,32 +1136,79 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>Moyenne</v>
+            <strRef>
+              <f>'TCD3'!B2</f>
+            </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="040459"/>
-            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="8"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="20B2AA"/>
+              </a:solidFill>
               <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="20B2AA"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <xVal>
             <numRef>
-              <f>'TCD2'!$A$22:$A$27</f>
+              <f>'TCD3'!$A$3:$A$12</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'TCD2'!$B$22:$B$27</f>
+              <f>'TCD3'!$B$3:$B$12</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'TCD3'!C2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF6B7B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF6B7B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'TCD3'!$A$3:$A$12</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'TCD3'!$C$3:$C$12</f>
             </numRef>
           </yVal>
         </ser>
@@ -1141,6 +1220,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1152,7 +1232,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Temps de sommeil (h)</a:t>
+                  <a:t>Temps de Sommeil (heures)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1167,6 +1247,146 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Niveau d'Addiction</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Performance Scolaire selon Stress par Genre</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'TCD3'!B16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4169E1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="4169E1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'TCD3'!$A$17:$A$26</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'TCD3'!$B$17:$B$26</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'TCD3'!C16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF1493"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF1493"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'TCD3'!$A$17:$A$26</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'TCD3'!$C$17:$C$26</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
         <title>
@@ -1178,7 +1398,365 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Niveau dépression</a:t>
+                  <a:t>Niveau de Stress</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Performance Scolaire</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Anxiété selon Temps d'Écran par Interaction sociale</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'TCD3'!B31</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="20B2AA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="20B2AA"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'TCD3'!$A$32:$A$38</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'TCD3'!$B$32:$B$38</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'TCD3'!C31</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF6B7B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF6B7B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'TCD3'!$A$32:$A$38</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'TCD3'!$C$32:$C$38</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Temps d'Écran avant Sommeil (heures)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Niveau d'Anxiété</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Performance Scolaire selon Sommeil par État Dépressif</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'TCD3'!B43</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="20B2AA"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="20B2AA"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'TCD3'!$A$44:$A$53</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'TCD3'!$B$44:$B$53</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'TCD3'!C43</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF6B7B"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF6B7B"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'TCD3'!$A$44:$A$53</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'TCD3'!$C$44:$C$53</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Temps de Sommeil (heures)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Performance Scolaire</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1273,7 +1851,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -1315,14 +1893,63 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3600000"/>
+    <ext cx="5040000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1337,6 +1964,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1344,7 +1993,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblGenres" displayName="tblGenres" ref="A1:A3" headerRowCount="1">
   <autoFilter ref="A1:A3"/>
   <tableColumns count="1">
-    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fdaa6651370&gt;"/>
+    <tableColumn id="1" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fda095d42f0&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1354,7 +2003,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblAges" displayName="tblAges" ref="C1:C8" headerRowCount="1">
   <autoFilter ref="C1:C8"/>
   <tableColumns count="1">
-    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fdaa6650650&gt;"/>
+    <tableColumn id="3" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fda095d4230&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1364,7 +2013,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblPlateformes" displayName="tblPlateformes" ref="E1:E4" headerRowCount="1">
   <autoFilter ref="E1:E4"/>
   <tableColumns count="1">
-    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fd8fe7134d0&gt;"/>
+    <tableColumn id="5" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fda095d7dd0&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1374,7 +2023,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblInteractions" displayName="tblInteractions" ref="G1:G4" headerRowCount="1">
   <autoFilter ref="G1:G4"/>
   <tableColumns count="1">
-    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fd8fe712150&gt;"/>
+    <tableColumn id="7" name="&lt;openpyxl.worksheet.formula.ArrayFormula object at 0x7fda095d6990&gt;"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1670,7 +2319,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AD20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1918,6 +2567,31 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Analyse des corrélations avancées (Santé Mentale)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:O1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1925,7 +2599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AH11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -58643,8 +59317,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Tableau de Bord 4 : Carte des Corrélations de Santé Mentale</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="38" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="C4" s="38" t="inlineStr">
+        <is>
+          <t>sleep_hours</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="inlineStr">
+        <is>
+          <t>daily_social_media_hours</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>academic_performance</t>
+        </is>
+      </c>
+      <c r="F4" s="38" t="inlineStr">
+        <is>
+          <t>physical_activity</t>
+        </is>
+      </c>
+      <c r="G4" s="38" t="inlineStr">
+        <is>
+          <t>social_num</t>
+        </is>
+      </c>
+      <c r="H4" s="38" t="inlineStr">
+        <is>
+          <t>stress_level</t>
+        </is>
+      </c>
+      <c r="I4" s="38" t="inlineStr">
+        <is>
+          <t>anxiety_level</t>
+        </is>
+      </c>
+      <c r="J4" s="38" t="inlineStr">
+        <is>
+          <t>addiction_level</t>
+        </is>
+      </c>
+      <c r="K4" s="38" t="inlineStr">
+        <is>
+          <t>depression_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B5" s="40">
+        <f>Correlations!B3</f>
+        <v/>
+      </c>
+      <c r="C5" s="40">
+        <f>Correlations!C3</f>
+        <v/>
+      </c>
+      <c r="D5" s="40">
+        <f>Correlations!D3</f>
+        <v/>
+      </c>
+      <c r="E5" s="40">
+        <f>Correlations!E3</f>
+        <v/>
+      </c>
+      <c r="F5" s="40">
+        <f>Correlations!F3</f>
+        <v/>
+      </c>
+      <c r="G5" s="40">
+        <f>Correlations!G3</f>
+        <v/>
+      </c>
+      <c r="H5" s="40">
+        <f>Correlations!H3</f>
+        <v/>
+      </c>
+      <c r="I5" s="40">
+        <f>Correlations!I3</f>
+        <v/>
+      </c>
+      <c r="J5" s="40">
+        <f>Correlations!J3</f>
+        <v/>
+      </c>
+      <c r="K5" s="40">
+        <f>Correlations!K3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>sleep_hours</t>
+        </is>
+      </c>
+      <c r="B6" s="40">
+        <f>Correlations!B4</f>
+        <v/>
+      </c>
+      <c r="C6" s="40">
+        <f>Correlations!C4</f>
+        <v/>
+      </c>
+      <c r="D6" s="40">
+        <f>Correlations!D4</f>
+        <v/>
+      </c>
+      <c r="E6" s="40">
+        <f>Correlations!E4</f>
+        <v/>
+      </c>
+      <c r="F6" s="40">
+        <f>Correlations!F4</f>
+        <v/>
+      </c>
+      <c r="G6" s="40">
+        <f>Correlations!G4</f>
+        <v/>
+      </c>
+      <c r="H6" s="40">
+        <f>Correlations!H4</f>
+        <v/>
+      </c>
+      <c r="I6" s="40">
+        <f>Correlations!I4</f>
+        <v/>
+      </c>
+      <c r="J6" s="40">
+        <f>Correlations!J4</f>
+        <v/>
+      </c>
+      <c r="K6" s="40">
+        <f>Correlations!K4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>daily_social_media_hours</t>
+        </is>
+      </c>
+      <c r="B7" s="40">
+        <f>Correlations!B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="40">
+        <f>Correlations!C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="40">
+        <f>Correlations!D5</f>
+        <v/>
+      </c>
+      <c r="E7" s="40">
+        <f>Correlations!E5</f>
+        <v/>
+      </c>
+      <c r="F7" s="40">
+        <f>Correlations!F5</f>
+        <v/>
+      </c>
+      <c r="G7" s="40">
+        <f>Correlations!G5</f>
+        <v/>
+      </c>
+      <c r="H7" s="40">
+        <f>Correlations!H5</f>
+        <v/>
+      </c>
+      <c r="I7" s="40">
+        <f>Correlations!I5</f>
+        <v/>
+      </c>
+      <c r="J7" s="40">
+        <f>Correlations!J5</f>
+        <v/>
+      </c>
+      <c r="K7" s="40">
+        <f>Correlations!K5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>academic_performance</t>
+        </is>
+      </c>
+      <c r="B8" s="40">
+        <f>Correlations!B6</f>
+        <v/>
+      </c>
+      <c r="C8" s="40">
+        <f>Correlations!C6</f>
+        <v/>
+      </c>
+      <c r="D8" s="40">
+        <f>Correlations!D6</f>
+        <v/>
+      </c>
+      <c r="E8" s="40">
+        <f>Correlations!E6</f>
+        <v/>
+      </c>
+      <c r="F8" s="40">
+        <f>Correlations!F6</f>
+        <v/>
+      </c>
+      <c r="G8" s="40">
+        <f>Correlations!G6</f>
+        <v/>
+      </c>
+      <c r="H8" s="40">
+        <f>Correlations!H6</f>
+        <v/>
+      </c>
+      <c r="I8" s="40">
+        <f>Correlations!I6</f>
+        <v/>
+      </c>
+      <c r="J8" s="40">
+        <f>Correlations!J6</f>
+        <v/>
+      </c>
+      <c r="K8" s="40">
+        <f>Correlations!K6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>physical_activity</t>
+        </is>
+      </c>
+      <c r="B9" s="40">
+        <f>Correlations!B7</f>
+        <v/>
+      </c>
+      <c r="C9" s="40">
+        <f>Correlations!C7</f>
+        <v/>
+      </c>
+      <c r="D9" s="40">
+        <f>Correlations!D7</f>
+        <v/>
+      </c>
+      <c r="E9" s="40">
+        <f>Correlations!E7</f>
+        <v/>
+      </c>
+      <c r="F9" s="40">
+        <f>Correlations!F7</f>
+        <v/>
+      </c>
+      <c r="G9" s="40">
+        <f>Correlations!G7</f>
+        <v/>
+      </c>
+      <c r="H9" s="40">
+        <f>Correlations!H7</f>
+        <v/>
+      </c>
+      <c r="I9" s="40">
+        <f>Correlations!I7</f>
+        <v/>
+      </c>
+      <c r="J9" s="40">
+        <f>Correlations!J7</f>
+        <v/>
+      </c>
+      <c r="K9" s="40">
+        <f>Correlations!K7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>social_num</t>
+        </is>
+      </c>
+      <c r="B10" s="40">
+        <f>Correlations!B8</f>
+        <v/>
+      </c>
+      <c r="C10" s="40">
+        <f>Correlations!C8</f>
+        <v/>
+      </c>
+      <c r="D10" s="40">
+        <f>Correlations!D8</f>
+        <v/>
+      </c>
+      <c r="E10" s="40">
+        <f>Correlations!E8</f>
+        <v/>
+      </c>
+      <c r="F10" s="40">
+        <f>Correlations!F8</f>
+        <v/>
+      </c>
+      <c r="G10" s="40">
+        <f>Correlations!G8</f>
+        <v/>
+      </c>
+      <c r="H10" s="40">
+        <f>Correlations!H8</f>
+        <v/>
+      </c>
+      <c r="I10" s="40">
+        <f>Correlations!I8</f>
+        <v/>
+      </c>
+      <c r="J10" s="40">
+        <f>Correlations!J8</f>
+        <v/>
+      </c>
+      <c r="K10" s="40">
+        <f>Correlations!K8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>stress_level</t>
+        </is>
+      </c>
+      <c r="B11" s="40">
+        <f>Correlations!B9</f>
+        <v/>
+      </c>
+      <c r="C11" s="40">
+        <f>Correlations!C9</f>
+        <v/>
+      </c>
+      <c r="D11" s="40">
+        <f>Correlations!D9</f>
+        <v/>
+      </c>
+      <c r="E11" s="40">
+        <f>Correlations!E9</f>
+        <v/>
+      </c>
+      <c r="F11" s="40">
+        <f>Correlations!F9</f>
+        <v/>
+      </c>
+      <c r="G11" s="40">
+        <f>Correlations!G9</f>
+        <v/>
+      </c>
+      <c r="H11" s="40">
+        <f>Correlations!H9</f>
+        <v/>
+      </c>
+      <c r="I11" s="40">
+        <f>Correlations!I9</f>
+        <v/>
+      </c>
+      <c r="J11" s="40">
+        <f>Correlations!J9</f>
+        <v/>
+      </c>
+      <c r="K11" s="40">
+        <f>Correlations!K9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>anxiety_level</t>
+        </is>
+      </c>
+      <c r="B12" s="40">
+        <f>Correlations!B10</f>
+        <v/>
+      </c>
+      <c r="C12" s="40">
+        <f>Correlations!C10</f>
+        <v/>
+      </c>
+      <c r="D12" s="40">
+        <f>Correlations!D10</f>
+        <v/>
+      </c>
+      <c r="E12" s="40">
+        <f>Correlations!E10</f>
+        <v/>
+      </c>
+      <c r="F12" s="40">
+        <f>Correlations!F10</f>
+        <v/>
+      </c>
+      <c r="G12" s="40">
+        <f>Correlations!G10</f>
+        <v/>
+      </c>
+      <c r="H12" s="40">
+        <f>Correlations!H10</f>
+        <v/>
+      </c>
+      <c r="I12" s="40">
+        <f>Correlations!I10</f>
+        <v/>
+      </c>
+      <c r="J12" s="40">
+        <f>Correlations!J10</f>
+        <v/>
+      </c>
+      <c r="K12" s="40">
+        <f>Correlations!K10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t>addiction_level</t>
+        </is>
+      </c>
+      <c r="B13" s="40">
+        <f>Correlations!B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="40">
+        <f>Correlations!C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="40">
+        <f>Correlations!D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="40">
+        <f>Correlations!E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="40">
+        <f>Correlations!F11</f>
+        <v/>
+      </c>
+      <c r="G13" s="40">
+        <f>Correlations!G11</f>
+        <v/>
+      </c>
+      <c r="H13" s="40">
+        <f>Correlations!H11</f>
+        <v/>
+      </c>
+      <c r="I13" s="40">
+        <f>Correlations!I11</f>
+        <v/>
+      </c>
+      <c r="J13" s="40">
+        <f>Correlations!J11</f>
+        <v/>
+      </c>
+      <c r="K13" s="40">
+        <f>Correlations!K11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>depression_label</t>
+        </is>
+      </c>
+      <c r="B14" s="40">
+        <f>Correlations!B12</f>
+        <v/>
+      </c>
+      <c r="C14" s="40">
+        <f>Correlations!C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="40">
+        <f>Correlations!D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="40">
+        <f>Correlations!E12</f>
+        <v/>
+      </c>
+      <c r="F14" s="40">
+        <f>Correlations!F12</f>
+        <v/>
+      </c>
+      <c r="G14" s="40">
+        <f>Correlations!G12</f>
+        <v/>
+      </c>
+      <c r="H14" s="40">
+        <f>Correlations!H12</f>
+        <v/>
+      </c>
+      <c r="I14" s="40">
+        <f>Correlations!I12</f>
+        <v/>
+      </c>
+      <c r="J14" s="40">
+        <f>Correlations!J12</f>
+        <v/>
+      </c>
+      <c r="K14" s="40">
+        <f>Correlations!K12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B5:K14">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="-1"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00FFF2F2"/>
+        <color rgb="00FFFFFF"/>
+        <color rgb="00E6F2FF"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -59098,7 +60343,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -59136,14 +60381,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -59847,14 +61092,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:M18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -59900,19 +61145,19 @@
           <t>Male</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "male", DATA!$F:$F, "&gt;="&amp;0, DATA!$F:$F, "&lt;"&amp;1, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
-      <c r="C3">
+      <c r="C3" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "male", DATA!$F:$F, "&gt;="&amp;1, DATA!$F:$F, "&lt;"&amp;2, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
-      <c r="D3">
+      <c r="D3" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "male", DATA!$F:$F, "&gt;="&amp;2, DATA!$F:$F, "&lt;"&amp;3, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
-      <c r="E3">
+      <c r="E3" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "male", DATA!$F:$F, "&gt;="&amp;3, DATA!$F:$F, "&lt;"&amp;4, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
@@ -59923,19 +61168,19 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "female", DATA!$F:$F, "&gt;="&amp;0, DATA!$F:$F, "&lt;"&amp;1, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
-      <c r="C4">
+      <c r="C4" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "female", DATA!$F:$F, "&gt;="&amp;1, DATA!$F:$F, "&lt;"&amp;2, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
-      <c r="D4">
+      <c r="D4" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "female", DATA!$F:$F, "&gt;="&amp;2, DATA!$F:$F, "&lt;"&amp;3, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
-      <c r="E4">
+      <c r="E4" s="30">
         <f>IFERROR(AVERAGEIFS(DATA!$G:$G, DATA!$B:$B, "female", DATA!$F:$F, "&gt;="&amp;3, DATA!$F:$F, "&lt;"&amp;4, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$D:$D, IF(TDB2!$J$3="Tous", "&lt;&gt;", TDB2!$J$3), DATA!$I:$I, IF(TDB2!$M$3="Tous", "&lt;&gt;", TDB2!$M$3)), 0)</f>
         <v/>
       </c>
@@ -60029,85 +61274,613 @@
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Données : Sommeil vs Dépression</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Sommeil (Milieu)</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr">
-        <is>
-          <t>Moyenne Dépression</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="B22">
-        <f>IFERROR(AVERAGEIFS(DATA!$M:$M, DATA!$E:$E, "&gt;="&amp;4, DATA!$E:$E, "&lt;"&amp;5, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$B:$B, IF(TDB2!$G$3="Tous", "&lt;&gt;", TDB2!$G$3)), 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="B23">
-        <f>IFERROR(AVERAGEIFS(DATA!$M:$M, DATA!$E:$E, "&gt;="&amp;5, DATA!$E:$E, "&lt;"&amp;6, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$B:$B, IF(TDB2!$G$3="Tous", "&lt;&gt;", TDB2!$G$3)), 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="B24">
-        <f>IFERROR(AVERAGEIFS(DATA!$M:$M, DATA!$E:$E, "&gt;="&amp;6, DATA!$E:$E, "&lt;"&amp;7, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$B:$B, IF(TDB2!$G$3="Tous", "&lt;&gt;", TDB2!$G$3)), 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="B25">
-        <f>IFERROR(AVERAGEIFS(DATA!$M:$M, DATA!$E:$E, "&gt;="&amp;7, DATA!$E:$E, "&lt;"&amp;8, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$B:$B, IF(TDB2!$G$3="Tous", "&lt;&gt;", TDB2!$G$3)), 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="B26">
-        <f>IFERROR(AVERAGEIFS(DATA!$M:$M, DATA!$E:$E, "&gt;="&amp;8, DATA!$E:$E, "&lt;"&amp;9, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$B:$B, IF(TDB2!$G$3="Tous", "&lt;&gt;", TDB2!$G$3)), 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="B27">
-        <f>IFERROR(AVERAGEIFS(DATA!$M:$M, DATA!$E:$E, "&gt;="&amp;9, DATA!$E:$E, "&lt;"&amp;10, DATA!$A:$A, IF(TDB2!$D$3="Tous", "&lt;&gt;", TDB2!$D$3), DATA!$B:$B, IF(TDB2!$G$3="Tous", "&lt;&gt;", TDB2!$G$3)), 0)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A20:B20"/>
+  <mergeCells count="2">
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="34" t="inlineStr">
+        <is>
+          <t>Sommeil vs Addiction par Interaction Sociale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Sommeil (h)</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>Addiction (Low)</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>Addiction (High)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C3" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B4" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C4" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C5" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B6" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C7" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B8" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C9" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B10" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C10" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B12" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C12" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$L$2:$L$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Performance vs Stress par Genre</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Stress</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Performance (Male)</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Performance (Female)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 1, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 1, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 2, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 2, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 3, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C19" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 3, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 4, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 4, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 5, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 5, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 6, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 6, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 7, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C23" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 7, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 8, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 8, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 9, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C25" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 9, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 10, DATA!$B$2:$B$1201, "male"), 0)</f>
+        <v/>
+      </c>
+      <c r="C26" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$J$2:$J$1201, 10, DATA!$B$2:$B$1201, "female"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>Anxiété vs Temps d'Écran par Interaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>Temps d'écran (h)</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>Anxiété (Low)</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>Anxiété (High)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B32" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(0.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(0.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C32" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(0.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(0.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(1.0-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(1.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C33" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(1.0-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(1.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B34" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(1.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(1.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C34" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(1.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(1.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(2.0-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(2.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C35" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(2.0-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(2.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B36" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(2.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(2.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C36" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(2.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(2.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(3.0-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(3.0+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C37" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(3.0-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(3.0+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B38" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(3.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(3.5+0.25), DATA!$I$2:$I$1201, "low"), 0)</f>
+        <v/>
+      </c>
+      <c r="C38" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$K$2:$K$1201, DATA!$F$2:$F$1201, "&gt;="&amp;(3.5-0.25), DATA!$F$2:$F$1201, "&lt;"&amp;(3.5+0.25), DATA!$I$2:$I$1201, "high"), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>Performance vs Sommeil par État Dépressif</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>Sommeil (h)</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Performance (No Dep)</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>Performance (Dep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.0+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C44" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.0+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B45" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.5+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C45" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(4.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(4.5+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.0+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C46" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.0+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B47" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.5+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C47" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(5.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(5.5+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.0+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C48" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.0+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B49" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.5+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C49" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(6.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(6.5+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.0+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C50" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.0+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B51" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.5+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C51" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(7.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(7.5+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.0+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C52" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.0-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.0+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B53" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.5+0.25), DATA!$M$2:$M$1201, 0), 0)</f>
+        <v/>
+      </c>
+      <c r="C53" s="7">
+        <f>IFERROR(AVERAGEIFS(DATA!$G$2:$G$1201, DATA!$E$2:$E$1201, "&gt;="&amp;(8.5-0.25), DATA!$E$2:$E$1201, "&lt;"&amp;(8.5+0.25), DATA!$M$2:$M$1201, 1), 0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>